--- a/Calibration_UWB/Erreur_UWB.xlsx
+++ b/Calibration_UWB/Erreur_UWB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Noé\Documents\GE5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Noé\Documents\GitHub\Projet-S-IoT-Essaim-de-Drone\Calibration_UWB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9BA209D-EC09-476C-B35C-D1694548ED86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6770E8C9-0622-427C-B1D7-0669F5352298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3432B3F7-2079-4B90-A4C0-F53B175D63F2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">Distance réelle (cm) </t>
   </si>
@@ -47,13 +47,16 @@
     <t>Distance mesurée</t>
   </si>
   <si>
-    <t>22 ticks</t>
-  </si>
-  <si>
     <t>Erreur</t>
   </si>
   <si>
     <t>Distance relative à 120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UWB 0 et 1 </t>
+  </si>
+  <si>
+    <t>9 ticks</t>
   </si>
 </sst>
 </file>
@@ -164,17 +167,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Feuil1!$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Erreur</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
             <a:ln w="38100" cap="rnd">
               <a:noFill/>
@@ -197,98 +189,179 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="4"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$B$2:$B$14</c:f>
+              <c:f>Feuil1!$B$15:$B$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>69.400000000000006</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>82.6</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>91</c:v>
+                  <c:v>135</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>100</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>107.3</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>120.5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>132</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>147.4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>155.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>164.7</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>167</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>176</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>189.6</c:v>
+                <c:pt idx="18">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>70</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$F$2:$F$14</c:f>
+              <c:f>Feuil1!$F$15:$F$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>8.4000000000000057</c:v>
+                  <c:v>1.4000000000000057</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.5</c:v>
+                  <c:v>-0.40000000000000568</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>-1.4000000000000057</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.5</c:v>
+                  <c:v>-1.4000000000000057</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.89999999999999147</c:v>
+                  <c:v>-9.9999999999994316E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.40000000000000568</c:v>
+                  <c:v>1.6999999999999886</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.6999999999999886</c:v>
+                  <c:v>5.3000000000000114</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.5999999999999943</c:v>
+                  <c:v>5.6999999999999886</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.5</c:v>
+                  <c:v>7.1999999999999886</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.1000000000000227</c:v>
+                  <c:v>7.1999999999999886</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.8000000000000114</c:v>
+                  <c:v>5.3000000000000114</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.8000000000000114</c:v>
+                  <c:v>4.3000000000000114</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.3000000000000114</c:v>
+                  <c:v>3.3000000000000114</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.9000000000000057</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1.5999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1.0999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-2.4000000000000057</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-3.2000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-2.7999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-3.4000000000000057</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-5.0999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-6.0999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-5.4000000000000057</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-7.7999999999999972</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -296,7 +369,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1AF6-4F6A-B0CE-CB144B01EBC5}"/>
+              <c16:uniqueId val="{00000000-4990-4947-841D-1F8F3874232F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -308,11 +381,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="175376240"/>
-        <c:axId val="1906350288"/>
+        <c:axId val="2109729584"/>
+        <c:axId val="2041907472"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="175376240"/>
+        <c:axId val="2109729584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -350,7 +423,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="0"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -369,12 +442,12 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1906350288"/>
+        <c:crossAx val="2041907472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1906350288"/>
+        <c:axId val="2041907472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -431,529 +504,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="175376240"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="fr-FR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="fr-FR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Feuil1!$G$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Distance relative à 120</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="power"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="log"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="fr-FR"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="2"/>
-            <c:intercept val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-4.7534995625546804E-3"/>
-                  <c:y val="-4.2844852726742509E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="fr-FR"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Feuil1!$G$2:$G$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>-50.599999999999994</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-37.400000000000006</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-29</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-20</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-12.700000000000003</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>27.400000000000006</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>35.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>44.699999999999989</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>47</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>69.599999999999994</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Feuil1!$F$2:$F$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>8.4000000000000057</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.89999999999999147</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.40000000000000568</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.6999999999999886</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.5999999999999943</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7.1000000000000227</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5.8000000000000114</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7.8000000000000114</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>8.3000000000000114</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-779F-48A2-8793-FD36AC4A3176}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="184338112"/>
-        <c:axId val="168932816"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="184338112"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="168932816"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="168932816"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="fr-FR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="184338112"/>
+        <c:crossAx val="2109729584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1042,46 +593,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -1598,543 +1109,27 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>358140</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>49530</xdr:rowOff>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>87630</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>49530</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>716280</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>87630</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Graphique 1">
+        <xdr:cNvPr id="5" name="Graphique 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE6D81A4-92E2-A77D-5084-7145BA487F78}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6D75911-D516-61E0-3E31-647C1226026C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2147,42 +1142,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>289560</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Graphique 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A4497C3-CF6C-E55F-C6A4-00FC377A3941}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2508,13 +1467,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3D655F8-00C4-4040-9A36-903A51E0E8F1}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="B1:J42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -2522,13 +1478,13 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="1">
         <v>69.400000000000006</v>
       </c>
@@ -2536,16 +1492,17 @@
       <c r="D2" s="1">
         <v>61</v>
       </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1">
-        <f>ABS(D2-B2)</f>
-        <v>8.4000000000000057</v>
-      </c>
-      <c r="G2">
+        <f>(D2-B2)</f>
+        <v>-8.4000000000000057</v>
+      </c>
+      <c r="G2" s="1">
         <f>B2-120</f>
         <v>-50.599999999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
         <v>82.6</v>
       </c>
@@ -2553,16 +1510,17 @@
       <c r="D3" s="1">
         <v>76.099999999999994</v>
       </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1">
-        <f t="shared" ref="F3:F14" si="0">ABS(D3-B3)</f>
-        <v>6.5</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G14" si="1">B3-120</f>
+        <f t="shared" ref="F3:F38" si="0">(D3-B3)</f>
+        <v>-6.5</v>
+      </c>
+      <c r="G3" s="1">
+        <f t="shared" ref="G3:G38" si="1">B3-120</f>
         <v>-37.400000000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>91</v>
       </c>
@@ -2570,16 +1528,17 @@
       <c r="D4" s="1">
         <v>87</v>
       </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G4">
+        <v>-4</v>
+      </c>
+      <c r="G4" s="1">
         <f t="shared" si="1"/>
         <v>-29</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>100</v>
       </c>
@@ -2587,16 +1546,17 @@
       <c r="D5" s="1">
         <v>96.5</v>
       </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="1">
         <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
-      <c r="G5">
+        <v>-3.5</v>
+      </c>
+      <c r="G5" s="1">
         <f t="shared" si="1"/>
         <v>-20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>107.3</v>
       </c>
@@ -2604,16 +1564,17 @@
       <c r="D6" s="1">
         <v>106.4</v>
       </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="1">
         <f t="shared" si="0"/>
-        <v>0.89999999999999147</v>
-      </c>
-      <c r="G6">
+        <v>-0.89999999999999147</v>
+      </c>
+      <c r="G6" s="1">
         <f t="shared" si="1"/>
         <v>-12.700000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>120.5</v>
       </c>
@@ -2621,16 +1582,23 @@
       <c r="D7" s="1">
         <v>120.9</v>
       </c>
+      <c r="E7" s="1"/>
       <c r="F7" s="1">
         <f t="shared" si="0"/>
         <v>0.40000000000000568</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>132</v>
       </c>
@@ -2638,16 +1606,17 @@
       <c r="D8" s="1">
         <v>133.69999999999999</v>
       </c>
+      <c r="E8" s="1"/>
       <c r="F8" s="1">
         <f t="shared" si="0"/>
         <v>1.6999999999999886</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>147.4</v>
       </c>
@@ -2655,16 +1624,17 @@
       <c r="D9" s="1">
         <v>150</v>
       </c>
+      <c r="E9" s="1"/>
       <c r="F9" s="1">
         <f t="shared" si="0"/>
         <v>2.5999999999999943</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <f t="shared" si="1"/>
         <v>27.400000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>155.5</v>
       </c>
@@ -2672,16 +1642,17 @@
       <c r="D10" s="1">
         <v>161</v>
       </c>
+      <c r="E10" s="1"/>
       <c r="F10" s="1">
         <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <f t="shared" si="1"/>
         <v>35.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>164.7</v>
       </c>
@@ -2689,16 +1660,17 @@
       <c r="D11" s="1">
         <v>171.8</v>
       </c>
+      <c r="E11" s="1"/>
       <c r="F11" s="1">
         <f t="shared" si="0"/>
         <v>7.1000000000000227</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <f t="shared" si="1"/>
         <v>44.699999999999989</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>167</v>
       </c>
@@ -2706,16 +1678,17 @@
       <c r="D12" s="1">
         <v>172.8</v>
       </c>
+      <c r="E12" s="1"/>
       <c r="F12" s="1">
         <f t="shared" si="0"/>
         <v>5.8000000000000114</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>176</v>
       </c>
@@ -2723,16 +1696,17 @@
       <c r="D13" s="1">
         <v>183.8</v>
       </c>
+      <c r="E13" s="1"/>
       <c r="F13" s="1">
         <f t="shared" si="0"/>
         <v>7.8000000000000114</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>189.6</v>
       </c>
@@ -2740,14 +1714,443 @@
       <c r="D14" s="1">
         <v>197.9</v>
       </c>
+      <c r="E14" s="1"/>
       <c r="F14" s="1">
         <f t="shared" si="0"/>
         <v>8.3000000000000114</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <f t="shared" si="1"/>
         <v>69.599999999999994</v>
       </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>125</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1">
+        <v>126.4</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <f t="shared" si="0"/>
+        <v>1.4000000000000057</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
+        <v>130</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1">
+        <v>129.6</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <f t="shared" si="0"/>
+        <v>-0.40000000000000568</v>
+      </c>
+      <c r="G16" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="1">
+        <v>135</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1">
+        <v>133.6</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <f t="shared" si="0"/>
+        <v>-1.4000000000000057</v>
+      </c>
+      <c r="G17" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="1">
+        <v>140</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1">
+        <v>138.6</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <f t="shared" si="0"/>
+        <v>-1.4000000000000057</v>
+      </c>
+      <c r="G18" s="1">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="1">
+        <v>145</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1">
+        <v>144.9</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1">
+        <f t="shared" si="0"/>
+        <v>-9.9999999999994316E-2</v>
+      </c>
+      <c r="G19" s="1">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="1">
+        <v>150</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1">
+        <v>151.69999999999999</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1">
+        <f t="shared" si="0"/>
+        <v>1.6999999999999886</v>
+      </c>
+      <c r="G20" s="1">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="1">
+        <v>155</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1">
+        <v>160.30000000000001</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1">
+        <f t="shared" si="0"/>
+        <v>5.3000000000000114</v>
+      </c>
+      <c r="G21" s="1">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="1">
+        <v>160</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1">
+        <v>165.7</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1">
+        <f t="shared" si="0"/>
+        <v>5.6999999999999886</v>
+      </c>
+      <c r="G22" s="1">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="1">
+        <v>165</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1">
+        <v>172.2</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1">
+        <f t="shared" si="0"/>
+        <v>7.1999999999999886</v>
+      </c>
+      <c r="G23" s="1">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="1">
+        <v>170</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1">
+        <v>177.2</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1">
+        <f t="shared" si="0"/>
+        <v>7.1999999999999886</v>
+      </c>
+      <c r="G24" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="1">
+        <v>175</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1">
+        <v>180.3</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1">
+        <f t="shared" si="0"/>
+        <v>5.3000000000000114</v>
+      </c>
+      <c r="G25" s="1">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="1">
+        <v>180</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1">
+        <v>184.3</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1">
+        <f t="shared" si="0"/>
+        <v>4.3000000000000114</v>
+      </c>
+      <c r="G26" s="1">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="1">
+        <v>185</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1">
+        <v>188.3</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1">
+        <f t="shared" si="0"/>
+        <v>3.3000000000000114</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="1">
+        <v>190</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1">
+        <v>191.9</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1">
+        <f t="shared" si="0"/>
+        <v>1.9000000000000057</v>
+      </c>
+      <c r="G28" s="1">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="1">
+        <v>115</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1">
+        <v>113.4</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1">
+        <f t="shared" si="0"/>
+        <v>-1.5999999999999943</v>
+      </c>
+      <c r="G29" s="1">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="1">
+        <v>110</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1">
+        <v>108.9</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1">
+        <f t="shared" si="0"/>
+        <v>-1.0999999999999943</v>
+      </c>
+      <c r="G30" s="1">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="1">
+        <v>105</v>
+      </c>
+      <c r="D31" s="1">
+        <v>102.6</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" si="0"/>
+        <v>-2.4000000000000057</v>
+      </c>
+      <c r="G31" s="1">
+        <f t="shared" si="1"/>
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="1">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>96.8</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" si="0"/>
+        <v>-3.2000000000000028</v>
+      </c>
+      <c r="G32" s="1">
+        <f t="shared" si="1"/>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="1">
+        <v>95</v>
+      </c>
+      <c r="D33" s="1">
+        <v>92.2</v>
+      </c>
+      <c r="F33" s="1">
+        <f t="shared" si="0"/>
+        <v>-2.7999999999999972</v>
+      </c>
+      <c r="G33" s="1">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="1">
+        <v>90</v>
+      </c>
+      <c r="D34" s="1">
+        <v>86.6</v>
+      </c>
+      <c r="F34" s="1">
+        <f t="shared" si="0"/>
+        <v>-3.4000000000000057</v>
+      </c>
+      <c r="G34" s="1">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="1">
+        <v>85</v>
+      </c>
+      <c r="D35" s="1">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="F35" s="1">
+        <f t="shared" si="0"/>
+        <v>-5.0999999999999943</v>
+      </c>
+      <c r="G35" s="1">
+        <f t="shared" si="1"/>
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="1">
+        <v>80</v>
+      </c>
+      <c r="D36" s="1">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="F36" s="1">
+        <f t="shared" si="0"/>
+        <v>-6.0999999999999943</v>
+      </c>
+      <c r="G36" s="1">
+        <f t="shared" si="1"/>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="1">
+        <v>75</v>
+      </c>
+      <c r="D37" s="1">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="F37" s="1">
+        <f t="shared" si="0"/>
+        <v>-5.4000000000000057</v>
+      </c>
+      <c r="G37" s="1">
+        <f t="shared" si="1"/>
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="1">
+        <v>70</v>
+      </c>
+      <c r="D38" s="1">
+        <v>62.2</v>
+      </c>
+      <c r="F38" s="1">
+        <f t="shared" si="0"/>
+        <v>-7.7999999999999972</v>
+      </c>
+      <c r="G38" s="1">
+        <f t="shared" si="1"/>
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="1"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="1"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="1"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
